--- a/Project Outputs for Eth_switch_1gbit/Документация/Перечень элементов.xlsx
+++ b/Project Outputs for Eth_switch_1gbit/Документация/Перечень элементов.xlsx
@@ -8,19 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shustrik\Documents\Altium\Eth_switch_1gbit\Project Outputs for Eth_switch_1gbit\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EEC5EF-FDF9-4850-8524-3BB26D29F546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF829D7-695F-463A-90D2-03D41144648D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1A64DD08-3B90-48DA-A5B7-27F148C384C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{832CA45F-5EC6-4950-A11D-480AE6642B5C}"/>
   </bookViews>
   <sheets>
     <sheet name="PER 1" sheetId="1" r:id="rId1"/>
     <sheet name="PER 2" sheetId="2" r:id="rId2"/>
-    <sheet name="PER 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'PER 1'!$A$1:$F$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'PER 2'!$A$1:$F$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'PER 3'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="87">
   <si>
     <t>Перв. примен.</t>
   </si>
@@ -76,40 +74,7 @@
     <t>Инв. № подл.</t>
   </si>
   <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Катушка индуктивности Индуктивность на 4,7 мкГн, номинальный </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ток 2,5 А B82462G4  </t>
-  </si>
-  <si>
-    <t>VD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диод Стабилитрон 10В, 2%, 0.5Вт mini_MELF_3.5mm  </t>
-  </si>
-  <si>
     <t>Конденсаторы</t>
-  </si>
-  <si>
-    <t>C26, C29, C30, C37, C38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Конденсатор 1210C  </t>
-  </si>
-  <si>
-    <t>C39, C40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Конденсатор 0603C  </t>
-  </si>
-  <si>
-    <t>C41, C42</t>
-  </si>
-  <si>
-    <t>C43...C48</t>
   </si>
   <si>
     <t>C1...C19, C21, C22, C24, C27, C28</t>
@@ -118,10 +83,22 @@
     <t xml:space="preserve">Конденсатор 0402C ёмкостью 0,1 мк 10%, 16 В, X7R 0402C  </t>
   </si>
   <si>
+    <t>C20, C23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конденсатор 0603C ёмкостью 22п 5%, 50 В, NP0 0603C  </t>
+  </si>
+  <si>
     <t>C25, C32...C35</t>
   </si>
   <si>
     <t xml:space="preserve">Конденсатор 0603C ёмкостью 0,1 мк 10%, 50 В, X7R 0603C  </t>
+  </si>
+  <si>
+    <t>C26, C29, C30, C37, C38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конденсатор 1210C  </t>
   </si>
   <si>
     <t>C31</t>
@@ -139,25 +116,67 @@
     <t xml:space="preserve">(10х10)мм SMD 460мА 2000часов 105°C ECAP_SMD_10,3x10,3  </t>
   </si>
   <si>
+    <t>C39, C40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конденсатор 0603C  </t>
+  </si>
+  <si>
+    <t>C41, C42</t>
+  </si>
+  <si>
+    <t>C43...C48</t>
+  </si>
+  <si>
+    <t>Микросхемы</t>
+  </si>
+  <si>
+    <t>DA1, DA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC-DC понижающий преобразователь, Vin: 3.8 - 40 В, adj, 2 А </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSOT26  </t>
+  </si>
+  <si>
+    <t>DD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Управляемый коммутатор второго уровня на 5+2 порта </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/100/1000M LQFP128_14x14_exposed_pad  </t>
+  </si>
+  <si>
+    <t>Катушки индуктивности</t>
+  </si>
+  <si>
     <t>L1</t>
   </si>
   <si>
-    <t xml:space="preserve">Катушка индуктивности Индуктивность на 2,2 мкГн, номинальный </t>
+    <t xml:space="preserve">Индуктивность на 2,2 мкГн, номинальный ток 2,5 А CDRH6D12  </t>
   </si>
   <si>
-    <t xml:space="preserve">ток 2,5 А CDRH6D12  </t>
+    <t>L2</t>
   </si>
   <si>
-    <t>C20, C23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Конденсатор Конденсатор 0603C ёмкостью 22п 5%, 50 В, NP0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603C  </t>
+    <t xml:space="preserve">Индуктивность на 4,7 мкГн, номинальный ток 2,5 А B82462G4  </t>
   </si>
   <si>
     <t>Резисторы</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1Вт 0603 2.49 кОм, 1%, Чип резистор 0603R  </t>
+  </si>
+  <si>
+    <t>R2, R19...R30, R32...R34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор номиналом 4,7 кОм 1% 0402R  </t>
   </si>
   <si>
     <t>R3...R18</t>
@@ -166,10 +185,43 @@
     <t xml:space="preserve">Резистор номиналом 1,0 кОм 1% 0402R  </t>
   </si>
   <si>
+    <t xml:space="preserve">   Взам. инв. №</t>
+  </si>
+  <si>
     <t>R31</t>
   </si>
   <si>
     <t xml:space="preserve">Резистор номиналом 1,0 МОм 1% 0603R  </t>
+  </si>
+  <si>
+    <t>R35...R42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор номиналом 470 Ом 1% 0402R  </t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор номиналом 10 кОм 1% 0603R  </t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор номиналом 750 Ом 1% 0603R  </t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор номиналом 2,0 кОм 1% 0603R  </t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор номиналом 5,6 кОм 1% 0603R  </t>
   </si>
   <si>
     <t>R47</t>
@@ -178,100 +230,37 @@
     <t xml:space="preserve">Резистор номиналом 1,8 кОм 1% 0603R  </t>
   </si>
   <si>
-    <t xml:space="preserve">   Взам. инв. №</t>
+    <t>Переключатели</t>
   </si>
   <si>
-    <t>R45</t>
+    <t>S1</t>
   </si>
   <si>
-    <t xml:space="preserve">Резистор номиналом 2,0 кОм 1% 0603R  </t>
+    <t xml:space="preserve">Тактовая кнопка Button_SMD_6x6  </t>
   </si>
   <si>
-    <t>R2, R19...R30, R32...R34</t>
+    <t>SB1, SB2</t>
   </si>
   <si>
-    <t xml:space="preserve">Резистор номиналом 4,7 кОм 1% 0402R  </t>
+    <t xml:space="preserve">Solder bridge, мост припоя, запаиваемая перемычка, net tie, </t>
   </si>
   <si>
-    <t>R46</t>
+    <t xml:space="preserve">jumper 0805SB  </t>
   </si>
   <si>
-    <t xml:space="preserve">Резистор номиналом 5,6 кОм 1% 0603R  </t>
-  </si>
-  <si>
-    <t>R43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор номиналом 10 кОм 1% 0603R  </t>
-  </si>
-  <si>
-    <t>R35...R42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор номиналом 470 Ом 1% 0402R  </t>
-  </si>
-  <si>
-    <t>R44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор номиналом 750 Ом 1% 0603R  </t>
-  </si>
-  <si>
-    <t>DD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Микросхема Управляемый коммутатор второго уровня на 5+2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">порта 10/100/1000M LQFP128_14x14_exposed_pad  </t>
+    <t>Диоды</t>
   </si>
   <si>
     <t>VD1</t>
   </si>
   <si>
-    <t xml:space="preserve">Диод Защитный диод на 12 В, рассеиваемая мощность 400 Вт SMA </t>
+    <t xml:space="preserve">Защитный диод на 12 В, рассеиваемая мощность 400 Вт SMA  </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>VD2</t>
   </si>
   <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Переключатель Тактовая кнопка Button_SMD_6x6  </t>
-  </si>
-  <si>
-    <t>ZQ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кварцевый резонатор Кварцевый резонатор SMD 25 МГц ±10ppm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD-3225_4P X322525MOB4SI  </t>
-  </si>
-  <si>
-    <t>DA1, DA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Микросхема DC-DC понижающий преобразователь, Vin: 3.8 - 40 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">В, adj, 2 А TSOT26  </t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор 0.1Вт 0603 2.49 кОм, 1%, Чип резистор 0603R  </t>
-  </si>
-  <si>
-    <t>SB1, SB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Переключатель Solder bridge, мост припоя, запаиваемая </t>
-  </si>
-  <si>
-    <t xml:space="preserve">перемычка, net tie, jumper 0805SB  </t>
+    <t xml:space="preserve">Стабилитрон 10В, 2%, 0.5Вт mini_MELF_3.5mm  </t>
   </si>
   <si>
     <t>VT1</t>
@@ -302,6 +291,15 @@
   </si>
   <si>
     <t xml:space="preserve">1 порт JK00136NL  </t>
+  </si>
+  <si>
+    <t>ZQ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кварцевый резонатор Кварцевый резонатор SMD 25 МГц ±10ppm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD-3225_4P X322525MOB4SI  </t>
   </si>
 </sst>
 </file>
@@ -765,7 +763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -922,12 +920,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -981,7 +983,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1" xr:uid="{11C211F9-DE02-458C-A291-C015108DBA44}"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{FCED5CF1-CFE9-4739-8652-6761BE1649A8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1224,80 +1226,8 @@
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
-<file path=xl/activeX/activeX61.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX62.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX63.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX64.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX65.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX66.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX67.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX68.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX69.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
 <file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX70.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX71.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX72.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX73.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX74.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX75.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX76.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX77.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX78.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{978C9E23-D4B0-11CE-BF2D-00AA003F40D0}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1328,7 +1258,7 @@
         <xdr:cNvPr id="2" name="Group 68">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77E3D314-1124-47FF-851D-432D784F729A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F37B9D1-366A-4C6F-9A90-6E5B6A88DF1F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1349,7 +1279,7 @@
           <xdr:cNvPr id="3" name="Line 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F021C3D-51CA-4C9E-B84C-6F7D43F0B939}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EABFF190-10FB-4745-BB73-26F6AAC83BE7}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1388,7 +1318,7 @@
           <xdr:cNvPr id="4" name="Line 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8CE2A71-5844-407A-BD2E-68A0A66A3B49}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB71A231-00D6-460D-9E40-2E9FF693313A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1427,7 +1357,7 @@
           <xdr:cNvPr id="5" name="Line 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{823ECFC2-36EB-42F3-B98D-DD77BB4168D4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CEBCAEE-9FFF-4CB8-B9CE-C9FCF1B8918A}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1466,7 +1396,7 @@
           <xdr:cNvPr id="6" name="Line 5">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F555E7A2-FCFE-4AC0-9198-4BF9C4634178}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F16CA23D-7A1A-4B3F-BCDC-ECCBF5960B64}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1505,7 +1435,7 @@
           <xdr:cNvPr id="7" name="Line 6">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E70FED4-4B41-40B6-9B68-2C72A24C3542}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57BD5BEF-7E32-47CF-95E0-D1EDC1296B60}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1544,7 +1474,7 @@
           <xdr:cNvPr id="8" name="Line 7">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE310EA-9010-42B2-B584-6767DE683399}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F89D49C7-D071-4629-B833-F800D86BC902}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1583,7 +1513,7 @@
           <xdr:cNvPr id="9" name="Line 8">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE3FD6E2-425B-46C0-95E3-165D0894FF6D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A430B63-7DB5-46B5-9690-1E230CFD752D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1622,7 +1552,7 @@
           <xdr:cNvPr id="10" name="Line 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22319CD7-207A-442E-878A-2688897C636B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD15D79E-663A-42A9-A297-4CBBF39E6467}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1661,7 +1591,7 @@
           <xdr:cNvPr id="11" name="Line 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{955466A9-6AFF-4317-A1B6-280F6114AC47}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE236D68-1E64-4137-80F9-F6A94E5C8424}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1700,7 +1630,7 @@
           <xdr:cNvPr id="12" name="Line 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C85EBA47-D9C7-4C88-94A9-D55EDF5FA9C1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73DFF19A-4D0D-416C-A55C-DFD31DCB6FF6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1739,7 +1669,7 @@
           <xdr:cNvPr id="13" name="Line 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C25299-7CDC-4904-B4A1-5B8A573BDB07}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{226DB0F1-AADB-46C0-A198-DE2FFB73D086}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1778,7 +1708,7 @@
           <xdr:cNvPr id="14" name="Line 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92C0C6FA-8217-457A-9F4B-A67158F2A462}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF9E3EE5-8DCF-4472-93B0-98E971AA75F6}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1817,7 +1747,7 @@
           <xdr:cNvPr id="15" name="Line 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC3AA3A-1783-4495-AEE4-E97619132DBA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB42C866-2EF9-4CA1-94A7-C1400749DC79}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1856,7 +1786,7 @@
           <xdr:cNvPr id="16" name="Line 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95B23332-C6E3-4156-8028-780F6524E258}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C810E65E-1643-4570-8DEF-9C58056D1F62}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1895,7 +1825,7 @@
           <xdr:cNvPr id="17" name="Line 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212FA42E-CC57-4363-A744-ACC114AE49AA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AB65DF8-71CA-4332-923F-2FB1B582F323}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1934,7 +1864,7 @@
           <xdr:cNvPr id="18" name="Line 39">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{132A48DC-FCC6-43D2-87A2-D1C91E1514F7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{484543DE-0B42-4629-9D26-4E6D3832A5CA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1973,7 +1903,7 @@
           <xdr:cNvPr id="19" name="Line 40">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFACA63F-C21B-499C-A4FB-DB86414EF07C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DD536FB-FCAF-4D31-8C3C-0CD936C6D3F0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2012,7 +1942,7 @@
           <xdr:cNvPr id="20" name="Line 41">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E973964D-ACA6-4968-8C13-2D87E3D346DE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE4F1454-9127-462F-9390-CC93EE9A86C0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2051,7 +1981,7 @@
           <xdr:cNvPr id="21" name="Line 42">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F84613B8-12FB-48DA-958E-864918E4FD54}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{545146A3-723A-4841-8FF5-E3331DC97284}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2090,7 +2020,7 @@
           <xdr:cNvPr id="22" name="Line 43">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{128DFB18-1182-4BF0-8C36-4A5B745FBF08}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C842E98-E6C0-4906-B14F-0A1A8C38ACE1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2129,7 +2059,7 @@
           <xdr:cNvPr id="23" name="Line 44">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EA71663-03E8-4F6F-A391-433136491CAF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82FD1221-BFAF-47A3-8909-B7ECDB6EA2A8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2168,7 +2098,7 @@
           <xdr:cNvPr id="24" name="Line 45">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFCF3EC2-7E87-43B3-BFB1-C76E6FA457AC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EB3EE4D-53DE-4977-9F87-B67837201578}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2228,7 +2158,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DB7308C-71E5-4AC3-BEC4-9FDC7EF15E55}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58EBDF9E-BCF3-483F-BAFC-9611873791CB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2299,7 +2229,7 @@
                   <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C54A6595-93DE-4E2E-B12D-5494499B8439}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB2460B6-4AFF-4C9B-9FE8-D4BC17D9F5C2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2370,7 +2300,7 @@
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A854FFCC-354F-4157-8F20-912D9220DF3C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C57175-C937-4615-BDD5-479567405427}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2441,7 +2371,7 @@
                   <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9D495B9-2126-4862-A947-61F7827EE970}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDF36B8-0899-4591-B236-0F69EE63DBA6}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2512,7 +2442,7 @@
                   <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F88A0637-0598-4465-9011-65229259C628}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC3E0E08-7C6F-499E-AE78-629425E8A99A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2583,7 +2513,7 @@
                   <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{245A975F-2296-47C6-9FBF-7A88B7DECD81}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA2C0AF-4DEA-4D30-B192-E9F3BA2F8EB6}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2654,7 +2584,7 @@
                   <a14:compatExt spid="_x0000_s1031"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C1142AA-12FB-43D5-B5C5-05DBAE8B80AA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E98D2E2-1D18-4F67-BB7F-4E618C689888}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2725,7 +2655,7 @@
                   <a14:compatExt spid="_x0000_s1032"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{438BB629-BD70-4697-9851-EC5D2C7CDB68}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03D904BB-54A4-40CA-96F8-6A00DF3C3840}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2796,7 +2726,7 @@
                   <a14:compatExt spid="_x0000_s1033"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A530692-3063-4ABF-B0EC-42F149120969}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E17482C-9FF3-4D26-B009-62D39CB660EA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2867,7 +2797,7 @@
                   <a14:compatExt spid="_x0000_s1034"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5534B968-F43F-4522-BA7E-736F6ECD3536}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4BC31C-7C0F-42C6-9191-E21C5B597158}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2938,7 +2868,7 @@
                   <a14:compatExt spid="_x0000_s1035"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{715909A7-C7B3-4C44-8741-8BAADAE8FBD7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64737FEF-AF4B-4573-B0C0-CA886C20F3B4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3009,7 +2939,7 @@
                   <a14:compatExt spid="_x0000_s1036"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A54A171-606C-4EDE-9B68-8A27D592F627}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59D77C48-C92B-4D6B-84CA-B70E8E19A7FA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3080,7 +3010,7 @@
                   <a14:compatExt spid="_x0000_s1037"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2877A49-29C1-4E29-AF5C-47A1C25A985A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6621D0AB-6A76-44D7-AD4E-2E408C5E8ECB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3151,7 +3081,7 @@
                   <a14:compatExt spid="_x0000_s1038"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF473575-24DF-4602-9211-701B225A6BC1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13AAD7DB-D585-41BD-B8C6-B055402E2E7F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3209,7 +3139,7 @@
                   <a14:compatExt spid="_x0000_s1039"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{448B93A5-0055-457E-80F1-CCA3EED4B75C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F7FE30-2BFF-4E15-AB46-281C4A133B5F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3267,7 +3197,7 @@
                   <a14:compatExt spid="_x0000_s1040"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A86424DD-3950-49A1-A854-85F0D90F5161}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB48557-1277-4577-9B07-BD84DD4B0580}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3325,7 +3255,7 @@
                   <a14:compatExt spid="_x0000_s1041"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B0805F-6714-4E2F-9C81-EB5836D05CFA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B11FCA23-BDBF-4533-A66A-F7A81E586E51}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3383,7 +3313,7 @@
                   <a14:compatExt spid="_x0000_s1042"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{906C6298-4D09-4A5C-99F4-E5A83B06562A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{487F6932-BD2D-4883-A56B-41EA7AC61652}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3454,7 +3384,7 @@
                   <a14:compatExt spid="_x0000_s1043"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783FFC65-25F0-4869-A140-DFF874D9E9BC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11553F5A-4941-4233-A605-DB4CAEB659FE}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3525,7 +3455,7 @@
                   <a14:compatExt spid="_x0000_s1044"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28D3F8F3-AD10-4332-850D-7142FC2CF1C1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7028554E-3974-42D5-B8AB-5E1CF269A0CD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3596,7 +3526,7 @@
                   <a14:compatExt spid="_x0000_s1045"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C69D0A01-FEE8-4C9E-9184-EAC0B75BF4A0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D55055EF-404A-4490-9972-92DCA83555DE}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3667,7 +3597,7 @@
                   <a14:compatExt spid="_x0000_s1046"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91BBA483-972A-49BC-A36A-FE4D560A4596}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DCF3B94-3038-415D-A03D-0522D2BCB7A1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3738,7 +3668,7 @@
                   <a14:compatExt spid="_x0000_s1047"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5101DC6-78FA-4E28-94ED-360CD54DB724}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C31E510A-FB2F-49A7-B048-45145DE2328F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3796,7 +3726,7 @@
                   <a14:compatExt spid="_x0000_s1048"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94F33E3-9868-4563-BBF5-77F3D7A1DF20}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB3F747-B9E4-4DA7-B676-CC84F185B9AD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3854,7 +3784,7 @@
                   <a14:compatExt spid="_x0000_s1049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6988F78-9E63-4914-BDD5-1026C6E5A57C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AC75769-6AD1-45A2-92AE-00DF76F421B9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3912,7 +3842,7 @@
                   <a14:compatExt spid="_x0000_s1050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62B02C2E-A6E0-4894-B427-79B8E9E11864}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2D4FFCA-1CFE-4F98-8681-105E299D649A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3970,7 +3900,7 @@
                   <a14:compatExt spid="_x0000_s1051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9CFA876-7470-4BCC-828A-A0324326A63C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD5CA502-9B4D-42F1-9F64-E8D492FECAEE}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4028,7 +3958,7 @@
                   <a14:compatExt spid="_x0000_s1052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BC53F30-1AA5-49B3-9FE4-4D8684A08842}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C9084D9-1763-4986-8A85-02509DEF492C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4086,7 +4016,7 @@
                   <a14:compatExt spid="_x0000_s1053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93C4DA00-72CF-4966-99F0-1B3AA647E5D9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F030679-CCCB-4AB0-B295-5B3AD887B82A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4144,7 +4074,7 @@
                   <a14:compatExt spid="_x0000_s1054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59A51D8D-6975-4E99-808B-7B1972BF548B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F730425-1CB2-47FC-ADC1-1A6B1B99D07A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4202,7 +4132,7 @@
                   <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4618738D-9D8D-42D7-84DA-1DE58F5FA673}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC4A9B0C-4442-46FC-8184-61AB81F006B0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4260,7 +4190,7 @@
                   <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C012A90A-AE38-4D17-9D42-C85E08EB6BA9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2972C63E-DDB9-48ED-9D97-33CE8912615C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4318,7 +4248,7 @@
                   <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{827934B1-53CE-4093-9B23-BFBC5AF1B576}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD3907F0-3487-4C58-B6B4-7602F20B0BA5}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4376,7 +4306,7 @@
                   <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06FCA78F-61D6-4D8F-8261-BFAD4728C4F6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED6492F8-7F3F-494A-91C8-35FE3325AA38}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4434,7 +4364,7 @@
                   <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE145D48-A655-4497-94D7-83833DCEDC8E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD443CAB-FA9A-46AC-BF76-68B986D025B1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4492,7 +4422,7 @@
                   <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA50D9D-E818-44FA-8279-63686270C843}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C85585-B9A9-4227-A94C-66F62B92394C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4550,7 +4480,7 @@
                   <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{481C1AF6-19BD-4389-9D1C-EAF3CA4B9219}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A64648B8-9844-4E14-9300-7F44AC32E7FD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4608,7 +4538,7 @@
                   <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FB0A250-6FCE-41CA-83B8-D7BF2B7A957F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8E31B4C-18BB-4FEA-AB75-E9DE587C3839}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4666,7 +4596,7 @@
                   <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D847F1B2-691D-4DDE-AD12-13D423CC7E52}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8984763-F6B8-4CF5-978C-22F0D9F14F7D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4724,7 +4654,7 @@
                   <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C374D99-F7AF-4D3B-B8B6-2583B11D6C5A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D60F00A5-2DD8-4DE1-9CE9-0A81783DF845}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4782,7 +4712,7 @@
                   <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B16155-D302-408B-A53E-00D2CDEE611D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F8A13F6-3CA8-49DD-9702-EC7BF18F66E7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4840,7 +4770,7 @@
                   <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5143B881-8F21-458E-98D4-C6C8D2BDB8CC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F03DC0E-E479-45F3-8333-8223E5F0158D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4893,7 +4823,7 @@
         <xdr:cNvPr id="67" name="Рисунок 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2984F9F0-AEF3-4387-B078-2095A2E9BC0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38CCB0FC-DCB4-4309-8799-55C6C3B8A4A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4972,7 +4902,7 @@
         <xdr:cNvPr id="2" name="Group 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC9EFBC6-5BA1-429F-A25A-74C036FF301F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6E4E1C5-6F12-4FBB-A1D4-8FA3ED910E1D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4993,7 +4923,7 @@
           <xdr:cNvPr id="3" name="Rectangle 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B42377B-F2AA-4A0A-8B8D-E7D30BBDB0A0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5806CC2F-1956-4884-98C5-40ABF2E5D0E0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5034,7 +4964,7 @@
           <xdr:cNvPr id="4" name="Line 11">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA6B4FC8-CD6B-4829-AB52-73F23034617B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5533745-FCC0-444E-91A4-592B8A26AEAA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5073,7 +5003,7 @@
           <xdr:cNvPr id="5" name="Line 12">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65C3A32D-9974-4CB0-B5D1-4DA36A25A745}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{093CEDE7-275E-4BB9-8F4A-28D02ABAEC08}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5112,7 +5042,7 @@
           <xdr:cNvPr id="6" name="Line 13">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{640CE34E-D57E-4D94-AF4F-2A63C813B7D0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5691FBC-D9F3-4160-AC9C-ED7663674FDC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5151,7 +5081,7 @@
           <xdr:cNvPr id="7" name="Line 14">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{365F3BD2-6680-451E-B1A0-9FE228B5E795}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18E59265-2AF3-4A49-9823-430D87913F8E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5190,7 +5120,7 @@
           <xdr:cNvPr id="8" name="Line 15">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB1838B7-11D8-4870-A4F6-2219A9BB2AB7}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80853B87-0042-454C-8112-B1078D055E6F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5229,7 +5159,7 @@
           <xdr:cNvPr id="9" name="Line 16">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE570B2A-8B3B-4669-98D7-4187994FE196}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED4475D1-F869-4CC7-9F06-36D5D055730F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5268,7 +5198,7 @@
           <xdr:cNvPr id="10" name="Line 17">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E89872E-5A18-42B3-A1A2-69D8990E943C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D49D733-8612-4BD3-AF14-8E3B9FBC8AD8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5307,7 +5237,7 @@
           <xdr:cNvPr id="11" name="Line 18">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{285FDA64-BD43-4645-99CE-A73F0CC726E8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61B8F3A3-D2F7-4A42-BF9A-F5B2CB46E5E5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5346,7 +5276,7 @@
           <xdr:cNvPr id="12" name="Line 19">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{183CA93D-80F6-46DB-871D-1A7826F2C475}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{989199E2-DAA8-4BB9-8ABD-627BF7F3B254}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5406,7 +5336,7 @@
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EAE2611-3666-4271-BFF9-8A6A0C8B9969}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{225E03E9-DCD2-4A3C-BDC0-A066FABA6AF9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5464,7 +5394,7 @@
                   <a14:compatExt spid="_x0000_s2050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C13B7397-8B24-431F-8372-5764C34DBFA8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1776031-2911-4DA0-A5DD-C365664A2F04}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5535,7 +5465,7 @@
                   <a14:compatExt spid="_x0000_s2051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BF16492-6A4E-45CE-B062-21F090D49E6C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90DFFC40-DC2E-4D03-B38B-1B2F5B1837EA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5606,7 +5536,7 @@
                   <a14:compatExt spid="_x0000_s2052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA9E9359-D0E8-4595-AFC2-CE0627DDC854}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35BB3F37-4168-4548-91A5-2936FC03AE6A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5677,7 +5607,7 @@
                   <a14:compatExt spid="_x0000_s2053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CDBB0EE-E11C-420A-84F8-E910996C98CE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B1C750C-F824-41B0-8769-2D9AD317B659}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5748,7 +5678,7 @@
                   <a14:compatExt spid="_x0000_s2054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BD3BFA3-9A88-42DF-A9C5-0C176A242DA3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64B90C71-2101-4E91-9B23-9DED74321983}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5819,7 +5749,7 @@
                   <a14:compatExt spid="_x0000_s2055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{247CEA3A-6140-4BC9-831E-D1D1B8EECDA7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FDBD61C-DB43-4277-B2B9-EBD54784BA03}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5890,7 +5820,7 @@
                   <a14:compatExt spid="_x0000_s2056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAC79343-4C5E-4F35-85CD-9FC7C0B01E06}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CE65003-9FE8-4D50-8EC9-656FD4C88C16}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5961,7 +5891,7 @@
                   <a14:compatExt spid="_x0000_s2057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{761290DF-50D5-44AA-9DFB-324DD660328B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68EABDA4-A30D-4493-9433-5BEA984CF096}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6019,7 +5949,7 @@
                   <a14:compatExt spid="_x0000_s2058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86DA13C8-4356-4ED8-9A96-06FDBF230EA7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30F5FE29-D382-4774-A118-5A60824FB0E4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6077,7 +6007,7 @@
                   <a14:compatExt spid="_x0000_s2059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{322DF921-2D0F-4DFF-85DF-49574F47B738}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97DEC6FF-84A4-46C0-9178-36FED5253431}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6135,7 +6065,7 @@
                   <a14:compatExt spid="_x0000_s2060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E83417-2D2F-4FB5-9330-86D0A1F58757}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D750DD65-DCAC-4821-B843-C77D59D0D1C3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6193,7 +6123,7 @@
                   <a14:compatExt spid="_x0000_s2061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FD523A8-3E36-42A1-B2F9-EBB7A4AD67B8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{593CCC35-E594-4983-A661-4F92DB219F0C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6251,7 +6181,7 @@
                   <a14:compatExt spid="_x0000_s2062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B07E25D-D862-4E3F-815E-1CAF8E157D27}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55F90A77-B283-442F-8B51-4F5226A7E711}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6309,7 +6239,7 @@
                   <a14:compatExt spid="_x0000_s2063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B117E9F-E553-444E-95F1-D29FCEE63A92}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9642042-C6E7-4343-AA78-B3A9AD0FE33D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6367,7 +6297,7 @@
                   <a14:compatExt spid="_x0000_s2064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FA05F0B-3902-4187-8681-442A7F5C909F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E125BA77-365A-49F6-8BA9-4F2527B085A4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6425,7 +6355,7 @@
                   <a14:compatExt spid="_x0000_s2065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E772AEA-655B-4309-892F-0279926A73AB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB2711AA-66D0-4668-90BC-571046356FCC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6483,1576 +6413,7 @@
                   <a14:compatExt spid="_x0000_s2066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{545B63FC-648A-4BC8-85F8-B42C7423A479}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="Group 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{897A8A8E-C43B-481B-81CE-305583C0A884}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr>
-          <a:grpSpLocks/>
-        </xdr:cNvGrpSpPr>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="390525" y="10306050"/>
-          <a:ext cx="6657975" cy="542925"/>
-          <a:chOff x="41" y="1082"/>
-          <a:chExt cx="699" cy="57"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="Rectangle 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EFCE598-F2AE-44C4-BE7B-4A88FF1D2872}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="41" y="1082"/>
-            <a:ext cx="699" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:miter lim="800000"/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="Line 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2FEA22F-12DB-48C4-8A8A-48E4BB185227}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="287" y="1082"/>
-            <a:ext cx="0" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="Line 12">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27AC72A1-0834-4276-91CA-DDA8ED6F0BD6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="249" y="1082"/>
-            <a:ext cx="0" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="Line 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80D19826-3D8D-47BC-AE9D-3F17D2D720B4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="192" y="1082"/>
-            <a:ext cx="0" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="Line 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E074AF8A-697E-4FDF-8CB9-270BD5B55C7C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="105" y="1082"/>
-            <a:ext cx="0" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="Line 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B64BD9B-DBE7-467A-AF61-C082C8BAB895}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="67" y="1082"/>
-            <a:ext cx="0" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="Line 16">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{321D1D56-BAA8-4187-B82F-67F1C0B499EC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="42" y="1101"/>
-            <a:ext cx="245" cy="0"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="9525">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="Line 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2EBB65C-8759-4365-9B84-F9489A8AD930}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="41" y="1120"/>
-            <a:ext cx="246" cy="0"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="Line 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26618425-3B99-4A89-A6BD-FAB9C6933C45}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="702" y="1082"/>
-            <a:ext cx="0" cy="57"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Line 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E39EBDB-F6AF-4008-8B30-5A0DF2D48E21}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks noChangeShapeType="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="702" y="1108"/>
-            <a:ext cx="38" cy="0"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="15875">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:noFill/>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1657350</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>142875</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1219200</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3073" name="Nomer_Docum" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54E6EA9F-C6FA-4FFB-A81E-41245F646F1C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>247650</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3074" name="Label6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F4ECCDE-952F-47A1-9FB4-8B120A869EC6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>590550</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3075" name="Label2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{144E1F2D-0CB2-4BD7-9C30-19CC13E1BDB2}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>628650</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>685800</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3076" name="Label3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DC003A7-341F-463D-B816-AAEFA307E3AA}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1238250</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3077" name="Label4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5C7801C-966C-4C24-8CCD-DCFF09A209E5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1276350</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1600200</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3078" name="Label5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64BE2DAE-3281-41C0-80D9-9846AD897706}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1276350</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1600200</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3079" name="Label1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55C4A5E1-4400-42EE-87B5-CD8B6DFB7783}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1295400</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1571625</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>95250</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3080" name="Page_number" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06CC3561-D050-44C0-82F0-50993E373D07}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="1">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="000000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3081" name="TextBox1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CE1856F-ACBC-4D5A-930B-5AA223842748}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>590550</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3082" name="TextBox2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4456151A-A6C2-4927-8EC8-1C2B9D93061A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>628650</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>704850</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3083" name="TextBox3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CFDC494-6F49-47B3-9C8B-8F50010C1F55}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1247775</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3084" name="TextBox4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB7ACD7D-0718-4F97-B814-577A9CDAB030}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1276350</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1609725</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3085" name="TextBox5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA3B208-E4EE-4B2B-BE05-183C3BA06ED6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3086" name="TextBox6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3086"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F5FA36F-3AC0-4E7A-9B2B-E4A745C9F788}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>590550</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3087" name="TextBox7" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3087"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A8BFA94-0640-4E6F-AB8B-AAE807515B65}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>628650</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>695325</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3088" name="TextBox8" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3088"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EB16ACE-EDB1-402C-9D07-4345BCF30A1C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1247775</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3089" name="TextBox9" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3089"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B56F74-A451-45A7-81F7-7C73C42634EF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1276350</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>1609725</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3090" name="TextBox10" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3090"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D6917AF-5347-4E52-B2C7-2303F4B5FC72}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DB72B9C-FAD5-4150-9038-B463AB7F20F1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8386,7 +6747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D670D09B-6024-4467-A86D-5BAB1E7166EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698807AB-FEAB-4FC2-BFA2-E0AD7C37EB3E}">
   <sheetPr codeName="Лист7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8864,45 +7225,53 @@
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="10">
-        <v>1</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="12"/>
+      <c r="C3" s="53" t="s">
+        <v>12</v>
+      </c>
       <c r="D3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
+      <c r="E3" s="14">
+        <v>1</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
+      <c r="C4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="17">
+        <v>1</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="12" t="s">
-        <v>14</v>
+      <c r="C5" s="53" t="s">
+        <v>16</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" s="14">
         <v>1</v>
@@ -8914,31 +7283,45 @@
     <row r="6" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
+      <c r="C6" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="21"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
+      <c r="C7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="22"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="53" t="s">
-        <v>17</v>
+      <c r="C8" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8" s="14">
         <v>1</v>
@@ -8950,27 +7333,21 @@
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="22"/>
       <c r="B9" s="23"/>
-      <c r="C9" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="C9" s="12"/>
       <c r="D9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>9</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22"/>
       <c r="B10" s="23"/>
       <c r="C10" s="12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
@@ -8983,10 +7360,10 @@
       <c r="A11" s="22"/>
       <c r="B11" s="23"/>
       <c r="C11" s="12" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
@@ -8998,11 +7375,11 @@
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="22"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="53" t="s">
-        <v>23</v>
+      <c r="C12" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
@@ -9014,43 +7391,29 @@
     <row r="13" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
       <c r="B13" s="25"/>
-      <c r="C13" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>9</v>
-      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="26"/>
       <c r="B14" s="26"/>
-      <c r="C14" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>9</v>
-      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="26"/>
       <c r="B15" s="26"/>
       <c r="C15" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="14">
         <v>1</v>
@@ -9064,7 +7427,7 @@
       <c r="B16" s="26"/>
       <c r="C16" s="12"/>
       <c r="D16" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="15"/>
@@ -9074,34 +7437,34 @@
         <v>6</v>
       </c>
       <c r="B17" s="28"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="14">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="29"/>
       <c r="B18" s="30"/>
-      <c r="C18" s="12" t="s">
-        <v>32</v>
-      </c>
+      <c r="C18" s="12"/>
       <c r="D18" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="14">
-        <v>1</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>9</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="29"/>
       <c r="B19" s="30"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="13" t="s">
-        <v>34</v>
-      </c>
+      <c r="D19" s="13"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
     </row>
@@ -9109,7 +7472,9 @@
       <c r="A20" s="29"/>
       <c r="B20" s="30"/>
       <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
+      <c r="D20" s="54" t="s">
+        <v>36</v>
+      </c>
       <c r="E20" s="14"/>
       <c r="F20" s="15"/>
     </row>
@@ -9119,10 +7484,10 @@
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E21" s="14">
         <v>1</v>
@@ -9134,12 +7499,18 @@
     <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="29"/>
       <c r="B22" s="30"/>
-      <c r="C22" s="12"/>
+      <c r="C22" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="D22" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="E22" s="14">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="33"/>
@@ -9155,8 +7526,8 @@
       </c>
       <c r="B24" s="30"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="52" t="s">
-        <v>38</v>
+      <c r="D24" s="54" t="s">
+        <v>41</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="15"/>
@@ -9165,10 +7536,10 @@
       <c r="A25" s="29"/>
       <c r="B25" s="30"/>
       <c r="C25" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E25" s="14">
         <v>1</v>
@@ -9180,11 +7551,11 @@
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="29"/>
       <c r="B26" s="30"/>
-      <c r="C26" s="12" t="s">
-        <v>41</v>
+      <c r="C26" s="53" t="s">
+        <v>44</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E26" s="14">
         <v>1</v>
@@ -9197,10 +7568,10 @@
       <c r="A27" s="29"/>
       <c r="B27" s="30"/>
       <c r="C27" s="12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E27" s="14">
         <v>1</v>
@@ -10380,7 +8751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2559A69-FEE7-470F-AB99-767F17972080}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DCA4B-AC58-4664-8535-C104E9799668}">
   <sheetPr codeName="Лист8">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10838,8 +9209,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54"/>
-      <c r="B1" s="55"/>
+      <c r="A1" s="55"/>
+      <c r="B1" s="56"/>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
@@ -10854,13 +9225,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="56"/>
-      <c r="B2" s="55"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="56"/>
       <c r="C2" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" s="10">
         <v>1</v>
@@ -10870,13 +9241,13 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="53" t="s">
-        <v>48</v>
+      <c r="A3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3" s="14">
         <v>1</v>
@@ -10886,13 +9257,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="56"/>
-      <c r="B4" s="55"/>
+      <c r="A4" s="57"/>
+      <c r="B4" s="56"/>
       <c r="C4" s="12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4" s="17">
         <v>1</v>
@@ -10902,13 +9273,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="56"/>
-      <c r="B5" s="55"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E5" s="14">
         <v>1</v>
@@ -10918,13 +9289,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="56"/>
-      <c r="B6" s="55"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E6" s="14">
         <v>1</v>
@@ -10934,13 +9305,13 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54"/>
-      <c r="B7" s="57"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" s="14">
         <v>1</v>
@@ -10950,55 +9321,63 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="54"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="54"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="55"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="54"/>
-      <c r="B10" s="57"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
-        <v>60</v>
+      <c r="D10" s="54" t="s">
+        <v>63</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="15"/>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="54"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="54"/>
-      <c r="B12" s="57"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="12" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" s="14">
         <v>1</v>
@@ -11008,55 +9387,57 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="54"/>
-      <c r="B13" s="57"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="12"/>
       <c r="D13" s="13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="12"/>
       <c r="D14" s="13"/>
       <c r="E14" s="14"/>
       <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="14">
-        <v>1</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>9</v>
-      </c>
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="14">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="54"/>
-      <c r="B17" s="57"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E17" s="14">
         <v>1</v>
@@ -11066,12 +9447,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="54"/>
-      <c r="B18" s="57"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="58"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="13" t="s">
-        <v>68</v>
-      </c>
+      <c r="D18" s="13"/>
       <c r="E18" s="14"/>
       <c r="F18" s="15"/>
     </row>
@@ -11079,80 +9458,84 @@
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="59"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="14">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="22"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="14">
-        <v>1</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>9</v>
-      </c>
+      <c r="B20" s="61"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="22"/>
-      <c r="B21" s="60"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="12"/>
-      <c r="D21" s="13" t="s">
-        <v>71</v>
+      <c r="D21" s="54" t="s">
+        <v>76</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="14">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="12" t="s">
-        <v>72</v>
-      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="12"/>
       <c r="D23" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="14">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>9</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="15"/>
     </row>
     <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="22"/>
-      <c r="B24" s="60"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
+      <c r="D24" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="E24" s="14"/>
       <c r="F24" s="15"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
-      <c r="B25" s="61"/>
+      <c r="B25" s="62"/>
       <c r="C25" s="12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E25" s="14">
         <v>1</v>
@@ -11163,19 +9546,19 @@
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="60"/>
+        <v>48</v>
+      </c>
+      <c r="B26" s="61"/>
       <c r="C26" s="12"/>
       <c r="D26" s="13" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="22"/>
-      <c r="B27" s="60"/>
+      <c r="B27" s="61"/>
       <c r="C27" s="12"/>
       <c r="D27" s="13"/>
       <c r="E27" s="14"/>
@@ -11183,12 +9566,12 @@
     </row>
     <row r="28" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
-      <c r="B28" s="60"/>
+      <c r="B28" s="61"/>
       <c r="C28" s="12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E28" s="14">
         <v>1</v>
@@ -11201,45 +9584,35 @@
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="59"/>
+      <c r="B29" s="60"/>
       <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
+      <c r="D29" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="E29" s="14"/>
       <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="22"/>
-      <c r="B30" s="62"/>
+      <c r="B30" s="63"/>
       <c r="C30" s="12"/>
-      <c r="D30" s="52" t="s">
-        <v>79</v>
-      </c>
+      <c r="D30" s="13"/>
       <c r="E30" s="14"/>
       <c r="F30" s="15"/>
     </row>
     <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="22"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="14">
-        <v>1</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>9</v>
-      </c>
+      <c r="B31" s="63"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
-      <c r="B32" s="63"/>
+      <c r="B32" s="64"/>
       <c r="C32" s="12"/>
-      <c r="D32" s="13" t="s">
-        <v>82</v>
-      </c>
+      <c r="D32" s="13"/>
       <c r="E32" s="14"/>
       <c r="F32" s="15"/>
     </row>
@@ -11247,23 +9620,23 @@
       <c r="A33" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68"/>
     </row>
     <row r="34" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="22"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="68"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="69"/>
       <c r="D34" s="39"/>
       <c r="E34" s="39"/>
       <c r="F34" s="40"/>
     </row>
     <row r="35" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="22"/>
-      <c r="B35" s="62"/>
+      <c r="B35" s="63"/>
       <c r="C35" s="41"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42"/>
@@ -11271,14 +9644,14 @@
     </row>
     <row r="36" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
-      <c r="B36" s="63"/>
+      <c r="B36" s="64"/>
       <c r="C36" s="48"/>
       <c r="D36" s="49"/>
       <c r="E36" s="49"/>
       <c r="F36" s="50"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D40" s="69"/>
+      <c r="D40" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -11756,1261 +10129,4 @@
     </mc:AlternateContent>
   </controls>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DA893B-60B2-4877-83DF-7EED8485A9C7}">
-  <sheetPr codeName="Лист9">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="2.5703125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="51" customWidth="1"/>
-    <col min="4" max="4" width="59.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="51" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" style="51" customWidth="1"/>
-    <col min="7" max="256" width="9.140625" style="5"/>
-    <col min="257" max="257" width="2.5703125" style="5" customWidth="1"/>
-    <col min="258" max="258" width="3.28515625" style="5" customWidth="1"/>
-    <col min="259" max="259" width="10.7109375" style="5" customWidth="1"/>
-    <col min="260" max="260" width="59.42578125" style="5" customWidth="1"/>
-    <col min="261" max="261" width="5.42578125" style="5" customWidth="1"/>
-    <col min="262" max="262" width="24.28515625" style="5" customWidth="1"/>
-    <col min="263" max="512" width="9.140625" style="5"/>
-    <col min="513" max="513" width="2.5703125" style="5" customWidth="1"/>
-    <col min="514" max="514" width="3.28515625" style="5" customWidth="1"/>
-    <col min="515" max="515" width="10.7109375" style="5" customWidth="1"/>
-    <col min="516" max="516" width="59.42578125" style="5" customWidth="1"/>
-    <col min="517" max="517" width="5.42578125" style="5" customWidth="1"/>
-    <col min="518" max="518" width="24.28515625" style="5" customWidth="1"/>
-    <col min="519" max="768" width="9.140625" style="5"/>
-    <col min="769" max="769" width="2.5703125" style="5" customWidth="1"/>
-    <col min="770" max="770" width="3.28515625" style="5" customWidth="1"/>
-    <col min="771" max="771" width="10.7109375" style="5" customWidth="1"/>
-    <col min="772" max="772" width="59.42578125" style="5" customWidth="1"/>
-    <col min="773" max="773" width="5.42578125" style="5" customWidth="1"/>
-    <col min="774" max="774" width="24.28515625" style="5" customWidth="1"/>
-    <col min="775" max="1024" width="9.140625" style="5"/>
-    <col min="1025" max="1025" width="2.5703125" style="5" customWidth="1"/>
-    <col min="1026" max="1026" width="3.28515625" style="5" customWidth="1"/>
-    <col min="1027" max="1027" width="10.7109375" style="5" customWidth="1"/>
-    <col min="1028" max="1028" width="59.42578125" style="5" customWidth="1"/>
-    <col min="1029" max="1029" width="5.42578125" style="5" customWidth="1"/>
-    <col min="1030" max="1030" width="24.28515625" style="5" customWidth="1"/>
-    <col min="1031" max="1280" width="9.140625" style="5"/>
-    <col min="1281" max="1281" width="2.5703125" style="5" customWidth="1"/>
-    <col min="1282" max="1282" width="3.28515625" style="5" customWidth="1"/>
-    <col min="1283" max="1283" width="10.7109375" style="5" customWidth="1"/>
-    <col min="1284" max="1284" width="59.42578125" style="5" customWidth="1"/>
-    <col min="1285" max="1285" width="5.42578125" style="5" customWidth="1"/>
-    <col min="1286" max="1286" width="24.28515625" style="5" customWidth="1"/>
-    <col min="1287" max="1536" width="9.140625" style="5"/>
-    <col min="1537" max="1537" width="2.5703125" style="5" customWidth="1"/>
-    <col min="1538" max="1538" width="3.28515625" style="5" customWidth="1"/>
-    <col min="1539" max="1539" width="10.7109375" style="5" customWidth="1"/>
-    <col min="1540" max="1540" width="59.42578125" style="5" customWidth="1"/>
-    <col min="1541" max="1541" width="5.42578125" style="5" customWidth="1"/>
-    <col min="1542" max="1542" width="24.28515625" style="5" customWidth="1"/>
-    <col min="1543" max="1792" width="9.140625" style="5"/>
-    <col min="1793" max="1793" width="2.5703125" style="5" customWidth="1"/>
-    <col min="1794" max="1794" width="3.28515625" style="5" customWidth="1"/>
-    <col min="1795" max="1795" width="10.7109375" style="5" customWidth="1"/>
-    <col min="1796" max="1796" width="59.42578125" style="5" customWidth="1"/>
-    <col min="1797" max="1797" width="5.42578125" style="5" customWidth="1"/>
-    <col min="1798" max="1798" width="24.28515625" style="5" customWidth="1"/>
-    <col min="1799" max="2048" width="9.140625" style="5"/>
-    <col min="2049" max="2049" width="2.5703125" style="5" customWidth="1"/>
-    <col min="2050" max="2050" width="3.28515625" style="5" customWidth="1"/>
-    <col min="2051" max="2051" width="10.7109375" style="5" customWidth="1"/>
-    <col min="2052" max="2052" width="59.42578125" style="5" customWidth="1"/>
-    <col min="2053" max="2053" width="5.42578125" style="5" customWidth="1"/>
-    <col min="2054" max="2054" width="24.28515625" style="5" customWidth="1"/>
-    <col min="2055" max="2304" width="9.140625" style="5"/>
-    <col min="2305" max="2305" width="2.5703125" style="5" customWidth="1"/>
-    <col min="2306" max="2306" width="3.28515625" style="5" customWidth="1"/>
-    <col min="2307" max="2307" width="10.7109375" style="5" customWidth="1"/>
-    <col min="2308" max="2308" width="59.42578125" style="5" customWidth="1"/>
-    <col min="2309" max="2309" width="5.42578125" style="5" customWidth="1"/>
-    <col min="2310" max="2310" width="24.28515625" style="5" customWidth="1"/>
-    <col min="2311" max="2560" width="9.140625" style="5"/>
-    <col min="2561" max="2561" width="2.5703125" style="5" customWidth="1"/>
-    <col min="2562" max="2562" width="3.28515625" style="5" customWidth="1"/>
-    <col min="2563" max="2563" width="10.7109375" style="5" customWidth="1"/>
-    <col min="2564" max="2564" width="59.42578125" style="5" customWidth="1"/>
-    <col min="2565" max="2565" width="5.42578125" style="5" customWidth="1"/>
-    <col min="2566" max="2566" width="24.28515625" style="5" customWidth="1"/>
-    <col min="2567" max="2816" width="9.140625" style="5"/>
-    <col min="2817" max="2817" width="2.5703125" style="5" customWidth="1"/>
-    <col min="2818" max="2818" width="3.28515625" style="5" customWidth="1"/>
-    <col min="2819" max="2819" width="10.7109375" style="5" customWidth="1"/>
-    <col min="2820" max="2820" width="59.42578125" style="5" customWidth="1"/>
-    <col min="2821" max="2821" width="5.42578125" style="5" customWidth="1"/>
-    <col min="2822" max="2822" width="24.28515625" style="5" customWidth="1"/>
-    <col min="2823" max="3072" width="9.140625" style="5"/>
-    <col min="3073" max="3073" width="2.5703125" style="5" customWidth="1"/>
-    <col min="3074" max="3074" width="3.28515625" style="5" customWidth="1"/>
-    <col min="3075" max="3075" width="10.7109375" style="5" customWidth="1"/>
-    <col min="3076" max="3076" width="59.42578125" style="5" customWidth="1"/>
-    <col min="3077" max="3077" width="5.42578125" style="5" customWidth="1"/>
-    <col min="3078" max="3078" width="24.28515625" style="5" customWidth="1"/>
-    <col min="3079" max="3328" width="9.140625" style="5"/>
-    <col min="3329" max="3329" width="2.5703125" style="5" customWidth="1"/>
-    <col min="3330" max="3330" width="3.28515625" style="5" customWidth="1"/>
-    <col min="3331" max="3331" width="10.7109375" style="5" customWidth="1"/>
-    <col min="3332" max="3332" width="59.42578125" style="5" customWidth="1"/>
-    <col min="3333" max="3333" width="5.42578125" style="5" customWidth="1"/>
-    <col min="3334" max="3334" width="24.28515625" style="5" customWidth="1"/>
-    <col min="3335" max="3584" width="9.140625" style="5"/>
-    <col min="3585" max="3585" width="2.5703125" style="5" customWidth="1"/>
-    <col min="3586" max="3586" width="3.28515625" style="5" customWidth="1"/>
-    <col min="3587" max="3587" width="10.7109375" style="5" customWidth="1"/>
-    <col min="3588" max="3588" width="59.42578125" style="5" customWidth="1"/>
-    <col min="3589" max="3589" width="5.42578125" style="5" customWidth="1"/>
-    <col min="3590" max="3590" width="24.28515625" style="5" customWidth="1"/>
-    <col min="3591" max="3840" width="9.140625" style="5"/>
-    <col min="3841" max="3841" width="2.5703125" style="5" customWidth="1"/>
-    <col min="3842" max="3842" width="3.28515625" style="5" customWidth="1"/>
-    <col min="3843" max="3843" width="10.7109375" style="5" customWidth="1"/>
-    <col min="3844" max="3844" width="59.42578125" style="5" customWidth="1"/>
-    <col min="3845" max="3845" width="5.42578125" style="5" customWidth="1"/>
-    <col min="3846" max="3846" width="24.28515625" style="5" customWidth="1"/>
-    <col min="3847" max="4096" width="9.140625" style="5"/>
-    <col min="4097" max="4097" width="2.5703125" style="5" customWidth="1"/>
-    <col min="4098" max="4098" width="3.28515625" style="5" customWidth="1"/>
-    <col min="4099" max="4099" width="10.7109375" style="5" customWidth="1"/>
-    <col min="4100" max="4100" width="59.42578125" style="5" customWidth="1"/>
-    <col min="4101" max="4101" width="5.42578125" style="5" customWidth="1"/>
-    <col min="4102" max="4102" width="24.28515625" style="5" customWidth="1"/>
-    <col min="4103" max="4352" width="9.140625" style="5"/>
-    <col min="4353" max="4353" width="2.5703125" style="5" customWidth="1"/>
-    <col min="4354" max="4354" width="3.28515625" style="5" customWidth="1"/>
-    <col min="4355" max="4355" width="10.7109375" style="5" customWidth="1"/>
-    <col min="4356" max="4356" width="59.42578125" style="5" customWidth="1"/>
-    <col min="4357" max="4357" width="5.42578125" style="5" customWidth="1"/>
-    <col min="4358" max="4358" width="24.28515625" style="5" customWidth="1"/>
-    <col min="4359" max="4608" width="9.140625" style="5"/>
-    <col min="4609" max="4609" width="2.5703125" style="5" customWidth="1"/>
-    <col min="4610" max="4610" width="3.28515625" style="5" customWidth="1"/>
-    <col min="4611" max="4611" width="10.7109375" style="5" customWidth="1"/>
-    <col min="4612" max="4612" width="59.42578125" style="5" customWidth="1"/>
-    <col min="4613" max="4613" width="5.42578125" style="5" customWidth="1"/>
-    <col min="4614" max="4614" width="24.28515625" style="5" customWidth="1"/>
-    <col min="4615" max="4864" width="9.140625" style="5"/>
-    <col min="4865" max="4865" width="2.5703125" style="5" customWidth="1"/>
-    <col min="4866" max="4866" width="3.28515625" style="5" customWidth="1"/>
-    <col min="4867" max="4867" width="10.7109375" style="5" customWidth="1"/>
-    <col min="4868" max="4868" width="59.42578125" style="5" customWidth="1"/>
-    <col min="4869" max="4869" width="5.42578125" style="5" customWidth="1"/>
-    <col min="4870" max="4870" width="24.28515625" style="5" customWidth="1"/>
-    <col min="4871" max="5120" width="9.140625" style="5"/>
-    <col min="5121" max="5121" width="2.5703125" style="5" customWidth="1"/>
-    <col min="5122" max="5122" width="3.28515625" style="5" customWidth="1"/>
-    <col min="5123" max="5123" width="10.7109375" style="5" customWidth="1"/>
-    <col min="5124" max="5124" width="59.42578125" style="5" customWidth="1"/>
-    <col min="5125" max="5125" width="5.42578125" style="5" customWidth="1"/>
-    <col min="5126" max="5126" width="24.28515625" style="5" customWidth="1"/>
-    <col min="5127" max="5376" width="9.140625" style="5"/>
-    <col min="5377" max="5377" width="2.5703125" style="5" customWidth="1"/>
-    <col min="5378" max="5378" width="3.28515625" style="5" customWidth="1"/>
-    <col min="5379" max="5379" width="10.7109375" style="5" customWidth="1"/>
-    <col min="5380" max="5380" width="59.42578125" style="5" customWidth="1"/>
-    <col min="5381" max="5381" width="5.42578125" style="5" customWidth="1"/>
-    <col min="5382" max="5382" width="24.28515625" style="5" customWidth="1"/>
-    <col min="5383" max="5632" width="9.140625" style="5"/>
-    <col min="5633" max="5633" width="2.5703125" style="5" customWidth="1"/>
-    <col min="5634" max="5634" width="3.28515625" style="5" customWidth="1"/>
-    <col min="5635" max="5635" width="10.7109375" style="5" customWidth="1"/>
-    <col min="5636" max="5636" width="59.42578125" style="5" customWidth="1"/>
-    <col min="5637" max="5637" width="5.42578125" style="5" customWidth="1"/>
-    <col min="5638" max="5638" width="24.28515625" style="5" customWidth="1"/>
-    <col min="5639" max="5888" width="9.140625" style="5"/>
-    <col min="5889" max="5889" width="2.5703125" style="5" customWidth="1"/>
-    <col min="5890" max="5890" width="3.28515625" style="5" customWidth="1"/>
-    <col min="5891" max="5891" width="10.7109375" style="5" customWidth="1"/>
-    <col min="5892" max="5892" width="59.42578125" style="5" customWidth="1"/>
-    <col min="5893" max="5893" width="5.42578125" style="5" customWidth="1"/>
-    <col min="5894" max="5894" width="24.28515625" style="5" customWidth="1"/>
-    <col min="5895" max="6144" width="9.140625" style="5"/>
-    <col min="6145" max="6145" width="2.5703125" style="5" customWidth="1"/>
-    <col min="6146" max="6146" width="3.28515625" style="5" customWidth="1"/>
-    <col min="6147" max="6147" width="10.7109375" style="5" customWidth="1"/>
-    <col min="6148" max="6148" width="59.42578125" style="5" customWidth="1"/>
-    <col min="6149" max="6149" width="5.42578125" style="5" customWidth="1"/>
-    <col min="6150" max="6150" width="24.28515625" style="5" customWidth="1"/>
-    <col min="6151" max="6400" width="9.140625" style="5"/>
-    <col min="6401" max="6401" width="2.5703125" style="5" customWidth="1"/>
-    <col min="6402" max="6402" width="3.28515625" style="5" customWidth="1"/>
-    <col min="6403" max="6403" width="10.7109375" style="5" customWidth="1"/>
-    <col min="6404" max="6404" width="59.42578125" style="5" customWidth="1"/>
-    <col min="6405" max="6405" width="5.42578125" style="5" customWidth="1"/>
-    <col min="6406" max="6406" width="24.28515625" style="5" customWidth="1"/>
-    <col min="6407" max="6656" width="9.140625" style="5"/>
-    <col min="6657" max="6657" width="2.5703125" style="5" customWidth="1"/>
-    <col min="6658" max="6658" width="3.28515625" style="5" customWidth="1"/>
-    <col min="6659" max="6659" width="10.7109375" style="5" customWidth="1"/>
-    <col min="6660" max="6660" width="59.42578125" style="5" customWidth="1"/>
-    <col min="6661" max="6661" width="5.42578125" style="5" customWidth="1"/>
-    <col min="6662" max="6662" width="24.28515625" style="5" customWidth="1"/>
-    <col min="6663" max="6912" width="9.140625" style="5"/>
-    <col min="6913" max="6913" width="2.5703125" style="5" customWidth="1"/>
-    <col min="6914" max="6914" width="3.28515625" style="5" customWidth="1"/>
-    <col min="6915" max="6915" width="10.7109375" style="5" customWidth="1"/>
-    <col min="6916" max="6916" width="59.42578125" style="5" customWidth="1"/>
-    <col min="6917" max="6917" width="5.42578125" style="5" customWidth="1"/>
-    <col min="6918" max="6918" width="24.28515625" style="5" customWidth="1"/>
-    <col min="6919" max="7168" width="9.140625" style="5"/>
-    <col min="7169" max="7169" width="2.5703125" style="5" customWidth="1"/>
-    <col min="7170" max="7170" width="3.28515625" style="5" customWidth="1"/>
-    <col min="7171" max="7171" width="10.7109375" style="5" customWidth="1"/>
-    <col min="7172" max="7172" width="59.42578125" style="5" customWidth="1"/>
-    <col min="7173" max="7173" width="5.42578125" style="5" customWidth="1"/>
-    <col min="7174" max="7174" width="24.28515625" style="5" customWidth="1"/>
-    <col min="7175" max="7424" width="9.140625" style="5"/>
-    <col min="7425" max="7425" width="2.5703125" style="5" customWidth="1"/>
-    <col min="7426" max="7426" width="3.28515625" style="5" customWidth="1"/>
-    <col min="7427" max="7427" width="10.7109375" style="5" customWidth="1"/>
-    <col min="7428" max="7428" width="59.42578125" style="5" customWidth="1"/>
-    <col min="7429" max="7429" width="5.42578125" style="5" customWidth="1"/>
-    <col min="7430" max="7430" width="24.28515625" style="5" customWidth="1"/>
-    <col min="7431" max="7680" width="9.140625" style="5"/>
-    <col min="7681" max="7681" width="2.5703125" style="5" customWidth="1"/>
-    <col min="7682" max="7682" width="3.28515625" style="5" customWidth="1"/>
-    <col min="7683" max="7683" width="10.7109375" style="5" customWidth="1"/>
-    <col min="7684" max="7684" width="59.42578125" style="5" customWidth="1"/>
-    <col min="7685" max="7685" width="5.42578125" style="5" customWidth="1"/>
-    <col min="7686" max="7686" width="24.28515625" style="5" customWidth="1"/>
-    <col min="7687" max="7936" width="9.140625" style="5"/>
-    <col min="7937" max="7937" width="2.5703125" style="5" customWidth="1"/>
-    <col min="7938" max="7938" width="3.28515625" style="5" customWidth="1"/>
-    <col min="7939" max="7939" width="10.7109375" style="5" customWidth="1"/>
-    <col min="7940" max="7940" width="59.42578125" style="5" customWidth="1"/>
-    <col min="7941" max="7941" width="5.42578125" style="5" customWidth="1"/>
-    <col min="7942" max="7942" width="24.28515625" style="5" customWidth="1"/>
-    <col min="7943" max="8192" width="9.140625" style="5"/>
-    <col min="8193" max="8193" width="2.5703125" style="5" customWidth="1"/>
-    <col min="8194" max="8194" width="3.28515625" style="5" customWidth="1"/>
-    <col min="8195" max="8195" width="10.7109375" style="5" customWidth="1"/>
-    <col min="8196" max="8196" width="59.42578125" style="5" customWidth="1"/>
-    <col min="8197" max="8197" width="5.42578125" style="5" customWidth="1"/>
-    <col min="8198" max="8198" width="24.28515625" style="5" customWidth="1"/>
-    <col min="8199" max="8448" width="9.140625" style="5"/>
-    <col min="8449" max="8449" width="2.5703125" style="5" customWidth="1"/>
-    <col min="8450" max="8450" width="3.28515625" style="5" customWidth="1"/>
-    <col min="8451" max="8451" width="10.7109375" style="5" customWidth="1"/>
-    <col min="8452" max="8452" width="59.42578125" style="5" customWidth="1"/>
-    <col min="8453" max="8453" width="5.42578125" style="5" customWidth="1"/>
-    <col min="8454" max="8454" width="24.28515625" style="5" customWidth="1"/>
-    <col min="8455" max="8704" width="9.140625" style="5"/>
-    <col min="8705" max="8705" width="2.5703125" style="5" customWidth="1"/>
-    <col min="8706" max="8706" width="3.28515625" style="5" customWidth="1"/>
-    <col min="8707" max="8707" width="10.7109375" style="5" customWidth="1"/>
-    <col min="8708" max="8708" width="59.42578125" style="5" customWidth="1"/>
-    <col min="8709" max="8709" width="5.42578125" style="5" customWidth="1"/>
-    <col min="8710" max="8710" width="24.28515625" style="5" customWidth="1"/>
-    <col min="8711" max="8960" width="9.140625" style="5"/>
-    <col min="8961" max="8961" width="2.5703125" style="5" customWidth="1"/>
-    <col min="8962" max="8962" width="3.28515625" style="5" customWidth="1"/>
-    <col min="8963" max="8963" width="10.7109375" style="5" customWidth="1"/>
-    <col min="8964" max="8964" width="59.42578125" style="5" customWidth="1"/>
-    <col min="8965" max="8965" width="5.42578125" style="5" customWidth="1"/>
-    <col min="8966" max="8966" width="24.28515625" style="5" customWidth="1"/>
-    <col min="8967" max="9216" width="9.140625" style="5"/>
-    <col min="9217" max="9217" width="2.5703125" style="5" customWidth="1"/>
-    <col min="9218" max="9218" width="3.28515625" style="5" customWidth="1"/>
-    <col min="9219" max="9219" width="10.7109375" style="5" customWidth="1"/>
-    <col min="9220" max="9220" width="59.42578125" style="5" customWidth="1"/>
-    <col min="9221" max="9221" width="5.42578125" style="5" customWidth="1"/>
-    <col min="9222" max="9222" width="24.28515625" style="5" customWidth="1"/>
-    <col min="9223" max="9472" width="9.140625" style="5"/>
-    <col min="9473" max="9473" width="2.5703125" style="5" customWidth="1"/>
-    <col min="9474" max="9474" width="3.28515625" style="5" customWidth="1"/>
-    <col min="9475" max="9475" width="10.7109375" style="5" customWidth="1"/>
-    <col min="9476" max="9476" width="59.42578125" style="5" customWidth="1"/>
-    <col min="9477" max="9477" width="5.42578125" style="5" customWidth="1"/>
-    <col min="9478" max="9478" width="24.28515625" style="5" customWidth="1"/>
-    <col min="9479" max="9728" width="9.140625" style="5"/>
-    <col min="9729" max="9729" width="2.5703125" style="5" customWidth="1"/>
-    <col min="9730" max="9730" width="3.28515625" style="5" customWidth="1"/>
-    <col min="9731" max="9731" width="10.7109375" style="5" customWidth="1"/>
-    <col min="9732" max="9732" width="59.42578125" style="5" customWidth="1"/>
-    <col min="9733" max="9733" width="5.42578125" style="5" customWidth="1"/>
-    <col min="9734" max="9734" width="24.28515625" style="5" customWidth="1"/>
-    <col min="9735" max="9984" width="9.140625" style="5"/>
-    <col min="9985" max="9985" width="2.5703125" style="5" customWidth="1"/>
-    <col min="9986" max="9986" width="3.28515625" style="5" customWidth="1"/>
-    <col min="9987" max="9987" width="10.7109375" style="5" customWidth="1"/>
-    <col min="9988" max="9988" width="59.42578125" style="5" customWidth="1"/>
-    <col min="9989" max="9989" width="5.42578125" style="5" customWidth="1"/>
-    <col min="9990" max="9990" width="24.28515625" style="5" customWidth="1"/>
-    <col min="9991" max="10240" width="9.140625" style="5"/>
-    <col min="10241" max="10241" width="2.5703125" style="5" customWidth="1"/>
-    <col min="10242" max="10242" width="3.28515625" style="5" customWidth="1"/>
-    <col min="10243" max="10243" width="10.7109375" style="5" customWidth="1"/>
-    <col min="10244" max="10244" width="59.42578125" style="5" customWidth="1"/>
-    <col min="10245" max="10245" width="5.42578125" style="5" customWidth="1"/>
-    <col min="10246" max="10246" width="24.28515625" style="5" customWidth="1"/>
-    <col min="10247" max="10496" width="9.140625" style="5"/>
-    <col min="10497" max="10497" width="2.5703125" style="5" customWidth="1"/>
-    <col min="10498" max="10498" width="3.28515625" style="5" customWidth="1"/>
-    <col min="10499" max="10499" width="10.7109375" style="5" customWidth="1"/>
-    <col min="10500" max="10500" width="59.42578125" style="5" customWidth="1"/>
-    <col min="10501" max="10501" width="5.42578125" style="5" customWidth="1"/>
-    <col min="10502" max="10502" width="24.28515625" style="5" customWidth="1"/>
-    <col min="10503" max="10752" width="9.140625" style="5"/>
-    <col min="10753" max="10753" width="2.5703125" style="5" customWidth="1"/>
-    <col min="10754" max="10754" width="3.28515625" style="5" customWidth="1"/>
-    <col min="10755" max="10755" width="10.7109375" style="5" customWidth="1"/>
-    <col min="10756" max="10756" width="59.42578125" style="5" customWidth="1"/>
-    <col min="10757" max="10757" width="5.42578125" style="5" customWidth="1"/>
-    <col min="10758" max="10758" width="24.28515625" style="5" customWidth="1"/>
-    <col min="10759" max="11008" width="9.140625" style="5"/>
-    <col min="11009" max="11009" width="2.5703125" style="5" customWidth="1"/>
-    <col min="11010" max="11010" width="3.28515625" style="5" customWidth="1"/>
-    <col min="11011" max="11011" width="10.7109375" style="5" customWidth="1"/>
-    <col min="11012" max="11012" width="59.42578125" style="5" customWidth="1"/>
-    <col min="11013" max="11013" width="5.42578125" style="5" customWidth="1"/>
-    <col min="11014" max="11014" width="24.28515625" style="5" customWidth="1"/>
-    <col min="11015" max="11264" width="9.140625" style="5"/>
-    <col min="11265" max="11265" width="2.5703125" style="5" customWidth="1"/>
-    <col min="11266" max="11266" width="3.28515625" style="5" customWidth="1"/>
-    <col min="11267" max="11267" width="10.7109375" style="5" customWidth="1"/>
-    <col min="11268" max="11268" width="59.42578125" style="5" customWidth="1"/>
-    <col min="11269" max="11269" width="5.42578125" style="5" customWidth="1"/>
-    <col min="11270" max="11270" width="24.28515625" style="5" customWidth="1"/>
-    <col min="11271" max="11520" width="9.140625" style="5"/>
-    <col min="11521" max="11521" width="2.5703125" style="5" customWidth="1"/>
-    <col min="11522" max="11522" width="3.28515625" style="5" customWidth="1"/>
-    <col min="11523" max="11523" width="10.7109375" style="5" customWidth="1"/>
-    <col min="11524" max="11524" width="59.42578125" style="5" customWidth="1"/>
-    <col min="11525" max="11525" width="5.42578125" style="5" customWidth="1"/>
-    <col min="11526" max="11526" width="24.28515625" style="5" customWidth="1"/>
-    <col min="11527" max="11776" width="9.140625" style="5"/>
-    <col min="11777" max="11777" width="2.5703125" style="5" customWidth="1"/>
-    <col min="11778" max="11778" width="3.28515625" style="5" customWidth="1"/>
-    <col min="11779" max="11779" width="10.7109375" style="5" customWidth="1"/>
-    <col min="11780" max="11780" width="59.42578125" style="5" customWidth="1"/>
-    <col min="11781" max="11781" width="5.42578125" style="5" customWidth="1"/>
-    <col min="11782" max="11782" width="24.28515625" style="5" customWidth="1"/>
-    <col min="11783" max="12032" width="9.140625" style="5"/>
-    <col min="12033" max="12033" width="2.5703125" style="5" customWidth="1"/>
-    <col min="12034" max="12034" width="3.28515625" style="5" customWidth="1"/>
-    <col min="12035" max="12035" width="10.7109375" style="5" customWidth="1"/>
-    <col min="12036" max="12036" width="59.42578125" style="5" customWidth="1"/>
-    <col min="12037" max="12037" width="5.42578125" style="5" customWidth="1"/>
-    <col min="12038" max="12038" width="24.28515625" style="5" customWidth="1"/>
-    <col min="12039" max="12288" width="9.140625" style="5"/>
-    <col min="12289" max="12289" width="2.5703125" style="5" customWidth="1"/>
-    <col min="12290" max="12290" width="3.28515625" style="5" customWidth="1"/>
-    <col min="12291" max="12291" width="10.7109375" style="5" customWidth="1"/>
-    <col min="12292" max="12292" width="59.42578125" style="5" customWidth="1"/>
-    <col min="12293" max="12293" width="5.42578125" style="5" customWidth="1"/>
-    <col min="12294" max="12294" width="24.28515625" style="5" customWidth="1"/>
-    <col min="12295" max="12544" width="9.140625" style="5"/>
-    <col min="12545" max="12545" width="2.5703125" style="5" customWidth="1"/>
-    <col min="12546" max="12546" width="3.28515625" style="5" customWidth="1"/>
-    <col min="12547" max="12547" width="10.7109375" style="5" customWidth="1"/>
-    <col min="12548" max="12548" width="59.42578125" style="5" customWidth="1"/>
-    <col min="12549" max="12549" width="5.42578125" style="5" customWidth="1"/>
-    <col min="12550" max="12550" width="24.28515625" style="5" customWidth="1"/>
-    <col min="12551" max="12800" width="9.140625" style="5"/>
-    <col min="12801" max="12801" width="2.5703125" style="5" customWidth="1"/>
-    <col min="12802" max="12802" width="3.28515625" style="5" customWidth="1"/>
-    <col min="12803" max="12803" width="10.7109375" style="5" customWidth="1"/>
-    <col min="12804" max="12804" width="59.42578125" style="5" customWidth="1"/>
-    <col min="12805" max="12805" width="5.42578125" style="5" customWidth="1"/>
-    <col min="12806" max="12806" width="24.28515625" style="5" customWidth="1"/>
-    <col min="12807" max="13056" width="9.140625" style="5"/>
-    <col min="13057" max="13057" width="2.5703125" style="5" customWidth="1"/>
-    <col min="13058" max="13058" width="3.28515625" style="5" customWidth="1"/>
-    <col min="13059" max="13059" width="10.7109375" style="5" customWidth="1"/>
-    <col min="13060" max="13060" width="59.42578125" style="5" customWidth="1"/>
-    <col min="13061" max="13061" width="5.42578125" style="5" customWidth="1"/>
-    <col min="13062" max="13062" width="24.28515625" style="5" customWidth="1"/>
-    <col min="13063" max="13312" width="9.140625" style="5"/>
-    <col min="13313" max="13313" width="2.5703125" style="5" customWidth="1"/>
-    <col min="13314" max="13314" width="3.28515625" style="5" customWidth="1"/>
-    <col min="13315" max="13315" width="10.7109375" style="5" customWidth="1"/>
-    <col min="13316" max="13316" width="59.42578125" style="5" customWidth="1"/>
-    <col min="13317" max="13317" width="5.42578125" style="5" customWidth="1"/>
-    <col min="13318" max="13318" width="24.28515625" style="5" customWidth="1"/>
-    <col min="13319" max="13568" width="9.140625" style="5"/>
-    <col min="13569" max="13569" width="2.5703125" style="5" customWidth="1"/>
-    <col min="13570" max="13570" width="3.28515625" style="5" customWidth="1"/>
-    <col min="13571" max="13571" width="10.7109375" style="5" customWidth="1"/>
-    <col min="13572" max="13572" width="59.42578125" style="5" customWidth="1"/>
-    <col min="13573" max="13573" width="5.42578125" style="5" customWidth="1"/>
-    <col min="13574" max="13574" width="24.28515625" style="5" customWidth="1"/>
-    <col min="13575" max="13824" width="9.140625" style="5"/>
-    <col min="13825" max="13825" width="2.5703125" style="5" customWidth="1"/>
-    <col min="13826" max="13826" width="3.28515625" style="5" customWidth="1"/>
-    <col min="13827" max="13827" width="10.7109375" style="5" customWidth="1"/>
-    <col min="13828" max="13828" width="59.42578125" style="5" customWidth="1"/>
-    <col min="13829" max="13829" width="5.42578125" style="5" customWidth="1"/>
-    <col min="13830" max="13830" width="24.28515625" style="5" customWidth="1"/>
-    <col min="13831" max="14080" width="9.140625" style="5"/>
-    <col min="14081" max="14081" width="2.5703125" style="5" customWidth="1"/>
-    <col min="14082" max="14082" width="3.28515625" style="5" customWidth="1"/>
-    <col min="14083" max="14083" width="10.7109375" style="5" customWidth="1"/>
-    <col min="14084" max="14084" width="59.42578125" style="5" customWidth="1"/>
-    <col min="14085" max="14085" width="5.42578125" style="5" customWidth="1"/>
-    <col min="14086" max="14086" width="24.28515625" style="5" customWidth="1"/>
-    <col min="14087" max="14336" width="9.140625" style="5"/>
-    <col min="14337" max="14337" width="2.5703125" style="5" customWidth="1"/>
-    <col min="14338" max="14338" width="3.28515625" style="5" customWidth="1"/>
-    <col min="14339" max="14339" width="10.7109375" style="5" customWidth="1"/>
-    <col min="14340" max="14340" width="59.42578125" style="5" customWidth="1"/>
-    <col min="14341" max="14341" width="5.42578125" style="5" customWidth="1"/>
-    <col min="14342" max="14342" width="24.28515625" style="5" customWidth="1"/>
-    <col min="14343" max="14592" width="9.140625" style="5"/>
-    <col min="14593" max="14593" width="2.5703125" style="5" customWidth="1"/>
-    <col min="14594" max="14594" width="3.28515625" style="5" customWidth="1"/>
-    <col min="14595" max="14595" width="10.7109375" style="5" customWidth="1"/>
-    <col min="14596" max="14596" width="59.42578125" style="5" customWidth="1"/>
-    <col min="14597" max="14597" width="5.42578125" style="5" customWidth="1"/>
-    <col min="14598" max="14598" width="24.28515625" style="5" customWidth="1"/>
-    <col min="14599" max="14848" width="9.140625" style="5"/>
-    <col min="14849" max="14849" width="2.5703125" style="5" customWidth="1"/>
-    <col min="14850" max="14850" width="3.28515625" style="5" customWidth="1"/>
-    <col min="14851" max="14851" width="10.7109375" style="5" customWidth="1"/>
-    <col min="14852" max="14852" width="59.42578125" style="5" customWidth="1"/>
-    <col min="14853" max="14853" width="5.42578125" style="5" customWidth="1"/>
-    <col min="14854" max="14854" width="24.28515625" style="5" customWidth="1"/>
-    <col min="14855" max="15104" width="9.140625" style="5"/>
-    <col min="15105" max="15105" width="2.5703125" style="5" customWidth="1"/>
-    <col min="15106" max="15106" width="3.28515625" style="5" customWidth="1"/>
-    <col min="15107" max="15107" width="10.7109375" style="5" customWidth="1"/>
-    <col min="15108" max="15108" width="59.42578125" style="5" customWidth="1"/>
-    <col min="15109" max="15109" width="5.42578125" style="5" customWidth="1"/>
-    <col min="15110" max="15110" width="24.28515625" style="5" customWidth="1"/>
-    <col min="15111" max="15360" width="9.140625" style="5"/>
-    <col min="15361" max="15361" width="2.5703125" style="5" customWidth="1"/>
-    <col min="15362" max="15362" width="3.28515625" style="5" customWidth="1"/>
-    <col min="15363" max="15363" width="10.7109375" style="5" customWidth="1"/>
-    <col min="15364" max="15364" width="59.42578125" style="5" customWidth="1"/>
-    <col min="15365" max="15365" width="5.42578125" style="5" customWidth="1"/>
-    <col min="15366" max="15366" width="24.28515625" style="5" customWidth="1"/>
-    <col min="15367" max="15616" width="9.140625" style="5"/>
-    <col min="15617" max="15617" width="2.5703125" style="5" customWidth="1"/>
-    <col min="15618" max="15618" width="3.28515625" style="5" customWidth="1"/>
-    <col min="15619" max="15619" width="10.7109375" style="5" customWidth="1"/>
-    <col min="15620" max="15620" width="59.42578125" style="5" customWidth="1"/>
-    <col min="15621" max="15621" width="5.42578125" style="5" customWidth="1"/>
-    <col min="15622" max="15622" width="24.28515625" style="5" customWidth="1"/>
-    <col min="15623" max="15872" width="9.140625" style="5"/>
-    <col min="15873" max="15873" width="2.5703125" style="5" customWidth="1"/>
-    <col min="15874" max="15874" width="3.28515625" style="5" customWidth="1"/>
-    <col min="15875" max="15875" width="10.7109375" style="5" customWidth="1"/>
-    <col min="15876" max="15876" width="59.42578125" style="5" customWidth="1"/>
-    <col min="15877" max="15877" width="5.42578125" style="5" customWidth="1"/>
-    <col min="15878" max="15878" width="24.28515625" style="5" customWidth="1"/>
-    <col min="15879" max="16128" width="9.140625" style="5"/>
-    <col min="16129" max="16129" width="2.5703125" style="5" customWidth="1"/>
-    <col min="16130" max="16130" width="3.28515625" style="5" customWidth="1"/>
-    <col min="16131" max="16131" width="10.7109375" style="5" customWidth="1"/>
-    <col min="16132" max="16132" width="59.42578125" style="5" customWidth="1"/>
-    <col min="16133" max="16133" width="5.42578125" style="5" customWidth="1"/>
-    <col min="16134" max="16134" width="24.28515625" style="5" customWidth="1"/>
-    <col min="16135" max="16384" width="9.140625" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="56"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-    </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="14">
-        <v>1</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="56"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="56"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="56"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-    </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-    </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="54"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
-    </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="54"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="54"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15"/>
-    </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="54"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
-    </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="54"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
-    </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="54"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15"/>
-    </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
-    </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="15"/>
-    </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-    </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="54"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="54"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="59"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
-    </row>
-    <row r="22" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
-    </row>
-    <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
-    </row>
-    <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="61"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
-    </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
-    </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="15"/>
-    </row>
-    <row r="28" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="15"/>
-    </row>
-    <row r="29" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="59"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
-    </row>
-    <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="15"/>
-    </row>
-    <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="15"/>
-    </row>
-    <row r="32" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
-    </row>
-    <row r="33" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67"/>
-    </row>
-    <row r="34" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-    </row>
-    <row r="35" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="43"/>
-    </row>
-    <row r="36" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="50"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D40" s="69"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="C34:F36"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="6" max="1048575" man="1"/>
-  </colBreaks>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3090" r:id="rId4" name="TextBox10">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1609725</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3090" r:id="rId4" name="TextBox10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3089" r:id="rId6" name="TextBox9">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>742950</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1247775</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3089" r:id="rId6" name="TextBox9"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3088" r:id="rId8" name="TextBox8">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>628650</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>695325</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3088" r:id="rId8" name="TextBox8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3087" r:id="rId10" name="TextBox7">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>590550</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3087" r:id="rId10" name="TextBox7"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3086" r:id="rId12" name="TextBox6">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3086" r:id="rId12" name="TextBox6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3085" r:id="rId14" name="TextBox5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1609725</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3085" r:id="rId14" name="TextBox5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3084" r:id="rId16" name="TextBox4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>742950</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1247775</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3084" r:id="rId16" name="TextBox4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3083" r:id="rId17" name="TextBox3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId18">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>628650</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>704850</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3083" r:id="rId17" name="TextBox3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3082" r:id="rId19" name="TextBox2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>590550</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3082" r:id="rId19" name="TextBox2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3081" r:id="rId20" name="TextBox1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3081" r:id="rId20" name="TextBox1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3080" r:id="rId21" name="Page_number">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId22">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1295400</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1571625</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3080" r:id="rId21" name="Page_number"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3079" r:id="rId23" name="Label1">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId24">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1600200</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3079" r:id="rId23" name="Label1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3078" r:id="rId25" name="Label5">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId26">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1600200</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3078" r:id="rId25" name="Label5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3077" r:id="rId27" name="Label4">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId28">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>742950</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1238250</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3077" r:id="rId27" name="Label4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3076" r:id="rId29" name="Label3">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId30">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>628650</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>685800</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3076" r:id="rId29" name="Label3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId31" name="Label2">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId32">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>590550</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3075" r:id="rId31" name="Label2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3074" r:id="rId33" name="Label6">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId34">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>247650</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3074" r:id="rId33" name="Label6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3073" r:id="rId35" name="Nomer_Docum">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId36">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1657350</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1219200</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3073" r:id="rId35" name="Nomer_Docum"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-</worksheet>
 </file>